--- a/Codes/TEXT_Extraction_Results_Upgraded.xlsx
+++ b/Codes/TEXT_Extraction_Results_Upgraded.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3B3BEF-7EBA-443C-AE05-2789C8B2763A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2A476F-EC30-479D-B5DB-887A1CD89ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EB23AC6-B6B0-4AA7-9373-EE0EE5D80F5D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="765">
   <si>
     <t>polymer</t>
   </si>
@@ -2325,6 +2325,12 @@
   </si>
   <si>
     <t>UV-VIS NER</t>
+  </si>
+  <si>
+    <t>Todo</t>
+  </si>
+  <si>
+    <t>add structure visual of the monomer</t>
   </si>
 </sst>
 </file>
@@ -2417,16 +2423,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>766457</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>842211</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>331030</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>80211</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>567474</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>88566</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>251620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>578424</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2449,8 +2455,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28078141" y="842211"/>
-          <a:ext cx="24706386" cy="15328566"/>
+          <a:off x="33859030" y="2257354"/>
+          <a:ext cx="11595519" cy="7029641"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2530,8 +2536,8 @@
     <xdr:to>
       <xdr:col>67</xdr:col>
       <xdr:colOff>452399</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1922142</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6058</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3082,9 +3088,10 @@
     <col min="10" max="10" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3122,7 +3129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3160,7 +3167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -3197,8 +3204,11 @@
       <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="O3" s="3" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -3235,8 +3245,11 @@
       <c r="L4" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="O4" s="3" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -3274,7 +3287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -3312,7 +3325,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>49</v>
       </c>
@@ -3350,7 +3363,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>53</v>
       </c>
@@ -3388,7 +3401,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -3426,7 +3439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -3464,7 +3477,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -3502,7 +3515,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -3540,7 +3553,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>87</v>
       </c>
@@ -3578,7 +3591,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>87</v>
       </c>
@@ -3616,7 +3629,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>105</v>
       </c>
@@ -3654,7 +3667,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>111</v>
       </c>
@@ -3844,7 +3857,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
@@ -3882,7 +3895,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -3920,7 +3933,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>145</v>
       </c>
@@ -3996,7 +4009,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>145</v>
       </c>
@@ -4034,7 +4047,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>163</v>
       </c>
@@ -4072,7 +4085,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>163</v>
       </c>
@@ -4113,7 +4126,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>163</v>
       </c>
@@ -4151,7 +4164,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>173</v>
       </c>
@@ -4192,7 +4205,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>173</v>
       </c>
@@ -4230,7 +4243,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>173</v>
       </c>
@@ -4268,7 +4281,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>174</v>
       </c>
@@ -4306,7 +4319,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>174</v>
       </c>
@@ -4344,7 +4357,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>174</v>
       </c>
@@ -4762,7 +4775,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>206</v>
       </c>
@@ -4800,7 +4813,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>206</v>
       </c>
@@ -4838,7 +4851,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>206</v>
       </c>
@@ -4876,7 +4889,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>12</v>
       </c>
@@ -4914,7 +4927,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>12</v>
       </c>
@@ -5028,7 +5041,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>12</v>
       </c>
@@ -5066,7 +5079,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>12</v>
       </c>
@@ -5180,7 +5193,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>234</v>
       </c>
@@ -5218,7 +5231,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>245</v>
       </c>
@@ -5256,7 +5269,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>252</v>
       </c>
@@ -5294,7 +5307,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>261</v>
       </c>
@@ -5332,7 +5345,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>264</v>
       </c>
@@ -5370,7 +5383,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>267</v>
       </c>
@@ -5408,7 +5421,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>273</v>
       </c>
@@ -5446,7 +5459,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>273</v>
       </c>
@@ -5484,7 +5497,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>273</v>
       </c>
@@ -5522,7 +5535,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>273</v>
       </c>
@@ -5560,7 +5573,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>273</v>
       </c>
@@ -5598,7 +5611,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>273</v>
       </c>
@@ -5636,7 +5649,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>273</v>
       </c>
@@ -5674,7 +5687,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>273</v>
       </c>
@@ -5712,7 +5725,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>273</v>
       </c>
@@ -5750,7 +5763,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>273</v>
       </c>
@@ -5788,7 +5801,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>234</v>
       </c>
@@ -5826,7 +5839,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>273</v>
       </c>
@@ -5864,7 +5877,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>273</v>
       </c>
@@ -5902,7 +5915,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>273</v>
       </c>
@@ -5940,7 +5953,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>273</v>
       </c>
@@ -5978,7 +5991,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>327</v>
       </c>
@@ -6016,7 +6029,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>330</v>
       </c>
@@ -6054,7 +6067,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>333</v>
       </c>
@@ -6092,7 +6105,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>252</v>
       </c>
@@ -6130,7 +6143,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>261</v>
       </c>
@@ -6168,7 +6181,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>264</v>
       </c>
@@ -6206,7 +6219,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>334</v>
       </c>
@@ -6244,7 +6257,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>343</v>
       </c>
@@ -6282,7 +6295,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>344</v>
       </c>
@@ -6320,7 +6333,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>345</v>
       </c>
@@ -6358,7 +6371,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>350</v>
       </c>
@@ -6396,7 +6409,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>350</v>
       </c>
@@ -6434,7 +6447,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>357</v>
       </c>
@@ -6472,7 +6485,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>361</v>
       </c>
@@ -6510,7 +6523,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>361</v>
       </c>
@@ -6548,7 +6561,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>366</v>
       </c>
@@ -6586,7 +6599,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>273</v>
       </c>
@@ -6624,7 +6637,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>273</v>
       </c>
@@ -6662,7 +6675,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>384</v>
       </c>
@@ -6700,7 +6713,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>384</v>
       </c>
@@ -6738,7 +6751,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>12</v>
       </c>
@@ -6776,7 +6789,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>401</v>
       </c>
@@ -6814,7 +6827,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>404</v>
       </c>
@@ -6852,7 +6865,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>410</v>
       </c>
@@ -6890,7 +6903,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>415</v>
       </c>
@@ -6928,7 +6941,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>417</v>
       </c>
@@ -6966,7 +6979,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>423</v>
       </c>
@@ -7004,7 +7017,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>428</v>
       </c>
@@ -7042,7 +7055,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>432</v>
       </c>
@@ -7080,7 +7093,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>273</v>
       </c>
@@ -7118,7 +7131,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>273</v>
       </c>
@@ -7156,7 +7169,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>273</v>
       </c>
@@ -7194,7 +7207,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>273</v>
       </c>
@@ -7232,7 +7245,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>196</v>
       </c>
@@ -7270,7 +7283,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>234</v>
       </c>
@@ -7308,7 +7321,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>455</v>
       </c>
@@ -7346,7 +7359,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>464</v>
       </c>
@@ -7384,7 +7397,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>466</v>
       </c>
@@ -7422,7 +7435,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>468</v>
       </c>
@@ -7460,7 +7473,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>474</v>
       </c>
@@ -7498,7 +7511,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>476</v>
       </c>
@@ -7536,7 +7549,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>478</v>
       </c>
@@ -7574,7 +7587,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>481</v>
       </c>
@@ -7612,7 +7625,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>273</v>
       </c>
@@ -7650,7 +7663,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>401</v>
       </c>
@@ -7688,7 +7701,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>489</v>
       </c>
@@ -7726,7 +7739,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>489</v>
       </c>
@@ -7764,7 +7777,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>489</v>
       </c>
@@ -7802,7 +7815,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>494</v>
       </c>
@@ -7840,7 +7853,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>495</v>
       </c>
@@ -7878,7 +7891,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>499</v>
       </c>
@@ -7916,7 +7929,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>506</v>
       </c>
@@ -7954,7 +7967,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>510</v>
       </c>
@@ -7992,7 +8005,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>515</v>
       </c>
@@ -8030,7 +8043,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>524</v>
       </c>
@@ -8068,7 +8081,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>532</v>
       </c>
@@ -8106,7 +8119,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>536</v>
       </c>
@@ -8144,7 +8157,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>532</v>
       </c>
@@ -8182,7 +8195,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>545</v>
       </c>
@@ -8220,7 +8233,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>532</v>
       </c>
@@ -8258,7 +8271,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>66</v>
       </c>
@@ -8296,7 +8309,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>564</v>
       </c>
@@ -8334,7 +8347,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>12</v>
       </c>
@@ -8372,7 +8385,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>573</v>
       </c>
@@ -8410,7 +8423,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>583</v>
       </c>
@@ -8448,7 +8461,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>583</v>
       </c>
@@ -8486,7 +8499,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>206</v>
       </c>
@@ -8524,7 +8537,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>273</v>
       </c>
@@ -8562,7 +8575,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>24</v>
       </c>
@@ -8600,7 +8613,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>605</v>
       </c>
@@ -8638,7 +8651,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>605</v>
       </c>
@@ -8676,7 +8689,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>605</v>
       </c>
@@ -8714,7 +8727,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>605</v>
       </c>
@@ -8752,7 +8765,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>12</v>
       </c>
@@ -8790,7 +8803,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>617</v>
       </c>
@@ -8828,7 +8841,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>621</v>
       </c>
@@ -8866,7 +8879,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>111</v>
       </c>
@@ -8904,7 +8917,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>489</v>
       </c>
@@ -8942,7 +8955,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>489</v>
       </c>
@@ -8980,7 +8993,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>489</v>
       </c>
@@ -9018,7 +9031,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>404</v>
       </c>
@@ -9056,7 +9069,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>273</v>
       </c>
@@ -9094,7 +9107,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>648</v>
       </c>
@@ -9132,7 +9145,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>273</v>
       </c>
@@ -9170,7 +9183,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>273</v>
       </c>
@@ -9208,7 +9221,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>657</v>
       </c>
@@ -9246,7 +9259,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>105</v>
       </c>
@@ -9284,7 +9297,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>87</v>
       </c>
@@ -9322,7 +9335,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>659</v>
       </c>
@@ -9360,7 +9373,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>660</v>
       </c>
@@ -9398,7 +9411,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>661</v>
       </c>
@@ -9436,7 +9449,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>116</v>
       </c>
@@ -9474,7 +9487,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>666</v>
       </c>
@@ -9512,7 +9525,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>273</v>
       </c>
@@ -9550,7 +9563,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>273</v>
       </c>
@@ -9588,7 +9601,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>657</v>
       </c>
@@ -9626,7 +9639,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>105</v>
       </c>
@@ -9664,7 +9677,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>87</v>
       </c>
@@ -9702,7 +9715,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>659</v>
       </c>
@@ -9740,7 +9753,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>660</v>
       </c>
@@ -9778,7 +9791,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>661</v>
       </c>
@@ -9816,7 +9829,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>661</v>
       </c>
@@ -9854,7 +9867,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>676</v>
       </c>
@@ -9892,7 +9905,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>661</v>
       </c>
@@ -9930,7 +9943,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>401</v>
       </c>
@@ -9968,7 +9981,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>12</v>
       </c>
@@ -10006,7 +10019,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>687</v>
       </c>
@@ -10044,7 +10057,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>688</v>
       </c>
@@ -10082,7 +10095,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>695</v>
       </c>
@@ -10120,7 +10133,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>404</v>
       </c>
@@ -10158,7 +10171,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>404</v>
       </c>
@@ -10196,7 +10209,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>704</v>
       </c>
@@ -10234,7 +10247,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>704</v>
       </c>
@@ -10272,7 +10285,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>706</v>
       </c>
@@ -10310,7 +10323,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>709</v>
       </c>
@@ -10348,7 +10361,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>713</v>
       </c>
@@ -10386,7 +10399,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>718</v>
       </c>
@@ -10424,7 +10437,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>404</v>
       </c>
@@ -10462,7 +10475,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>729</v>
       </c>
@@ -10500,7 +10513,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>605</v>
       </c>
@@ -10538,7 +10551,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>605</v>
       </c>
@@ -10576,7 +10589,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>605</v>
       </c>
@@ -10614,7 +10627,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>605</v>
       </c>
@@ -10652,7 +10665,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>605</v>
       </c>
@@ -10690,7 +10703,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>404</v>
       </c>
@@ -10728,7 +10741,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>744</v>
       </c>
@@ -10766,7 +10779,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>474</v>
       </c>
@@ -10804,7 +10817,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>747</v>
       </c>
@@ -10842,7 +10855,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>401</v>
       </c>
@@ -10880,7 +10893,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>753</v>
       </c>
@@ -10918,7 +10931,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>757</v>
       </c>

--- a/Codes/TEXT_Extraction_Results_Upgraded.xlsx
+++ b/Codes/TEXT_Extraction_Results_Upgraded.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2A476F-EC30-479D-B5DB-887A1CD89ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B415F48B-B7FD-4E1A-A9A2-4CC65B172937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EB23AC6-B6B0-4AA7-9373-EE0EE5D80F5D}"/>
   </bookViews>
@@ -2430,9 +2430,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>251620</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>578424</xdr:rowOff>
+      <xdr:colOff>251619</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>367658</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2467,16 +2467,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>136636</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>248157</xdr:rowOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>179311</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>91848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>64</xdr:col>
-      <xdr:colOff>390637</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>16510</xdr:rowOff>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>667905</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>78450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2506,8 +2506,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="55557482" y="8659465"/>
-          <a:ext cx="17516232" cy="9762276"/>
+          <a:off x="69661679" y="5165164"/>
+          <a:ext cx="9512279" cy="5220339"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2528,16 +2528,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>895745</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>629139</xdr:rowOff>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>757948</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>516525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>67</xdr:col>
-      <xdr:colOff>452399</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>6058</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>819587</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>293565</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2560,8 +2560,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="64187927" y="1714412"/>
-          <a:ext cx="11263745" cy="6419185"/>
+          <a:off x="73849790" y="1799893"/>
+          <a:ext cx="6378218" cy="2845093"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2572,16 +2572,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>65</xdr:col>
-      <xdr:colOff>280786</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>689631</xdr:rowOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>20102</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>161444</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>72</xdr:col>
-      <xdr:colOff>497738</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>248295</xdr:rowOff>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>481778</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>228241</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2611,8 +2611,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="73872401" y="10185323"/>
-          <a:ext cx="6576722" cy="7002818"/>
+          <a:off x="79428523" y="5956655"/>
+          <a:ext cx="4071150" cy="3495797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2636,13 +2636,13 @@
       <xdr:col>53</xdr:col>
       <xdr:colOff>392546</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>588818</xdr:rowOff>
+      <xdr:rowOff>192578</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>68</xdr:col>
       <xdr:colOff>854363</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>65352</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>332154</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2657,8 +2657,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="62784182" y="588818"/>
-          <a:ext cx="13969999" cy="1300716"/>
+          <a:off x="70652854" y="192578"/>
+          <a:ext cx="13943355" cy="1429114"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2719,8 +2719,8 @@
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>362857</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>151685</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>281387</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3076,22 +3076,23 @@
   <dimension ref="A1:AM207"/>
   <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.44140625" customWidth="1"/>
+    <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="61.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3249,7 +3250,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>49</v>
       </c>
@@ -3477,7 +3478,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -3629,7 +3630,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>105</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -3743,7 +3744,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>116</v>
       </c>
@@ -3781,7 +3782,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>116</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -3971,7 +3972,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>145</v>
       </c>
@@ -4047,7 +4048,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>163</v>
       </c>
@@ -4085,7 +4086,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>163</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>163</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>173</v>
       </c>
@@ -4205,7 +4206,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>173</v>
       </c>
@@ -4243,7 +4244,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>173</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>174</v>
       </c>
@@ -4319,7 +4320,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>174</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>174</v>
       </c>
@@ -4395,7 +4396,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>189</v>
       </c>
@@ -4433,7 +4434,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>194</v>
       </c>
@@ -4471,7 +4472,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>196</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>197</v>
       </c>
@@ -4547,7 +4548,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>198</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>199</v>
       </c>
@@ -4623,7 +4624,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>200</v>
       </c>
@@ -4661,7 +4662,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>201</v>
       </c>
@@ -4699,7 +4700,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>202</v>
       </c>
@@ -4737,7 +4738,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>205</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>206</v>
       </c>
@@ -4813,7 +4814,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>206</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>206</v>
       </c>
@@ -4889,7 +4890,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>12</v>
       </c>
@@ -4927,7 +4928,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>12</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>12</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>12</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>12</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>12</v>
       </c>
@@ -5269,7 +5270,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>252</v>
       </c>
@@ -5307,7 +5308,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>261</v>
       </c>
@@ -5649,7 +5650,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>273</v>
       </c>
@@ -6105,7 +6106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>252</v>
       </c>
@@ -6143,7 +6144,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>261</v>
       </c>
@@ -6675,7 +6676,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>384</v>
       </c>
@@ -6713,7 +6714,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>384</v>
       </c>
@@ -7929,7 +7930,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>506</v>
       </c>
@@ -8119,7 +8120,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>536</v>
       </c>
@@ -8309,7 +8310,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>564</v>
       </c>
@@ -8385,7 +8386,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>573</v>
       </c>
@@ -8499,7 +8500,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>206</v>
       </c>
@@ -9069,7 +9070,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>273</v>
       </c>
@@ -9107,7 +9108,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>648</v>
       </c>
@@ -9411,7 +9412,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>661</v>
       </c>
@@ -9791,7 +9792,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>661</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>676</v>
       </c>
@@ -10323,7 +10324,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>709</v>
       </c>
@@ -10399,7 +10400,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>718</v>
       </c>
@@ -10437,7 +10438,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>404</v>
       </c>

--- a/Codes/TEXT_Extraction_Results_Upgraded.xlsx
+++ b/Codes/TEXT_Extraction_Results_Upgraded.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B415F48B-B7FD-4E1A-A9A2-4CC65B172937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86A76B2-2FE7-4A60-BF22-903F4885A6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EB23AC6-B6B0-4AA7-9373-EE0EE5D80F5D}"/>
   </bookViews>
@@ -35,8 +35,80 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="6">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="6">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="771">
   <si>
     <t>polymer</t>
   </si>
@@ -2331,6 +2403,24 @@
   </si>
   <si>
     <t>add structure visual of the monomer</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>3D</t>
+  </si>
+  <si>
+    <t>SMILES Representations</t>
+  </si>
+  <si>
+    <t>CCCCCCc1ccsc1</t>
+  </si>
+  <si>
+    <t>C1COC2=CSC=C2O1</t>
+  </si>
+  <si>
+    <t>Cc1ccc(cc1)S(=O)(=O)[O-]</t>
   </si>
 </sst>
 </file>
@@ -2423,16 +2513,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>331030</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>80211</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>251619</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>367658</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>251618</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1573742</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2467,16 +2557,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>52</xdr:col>
+      <xdr:col>55</xdr:col>
       <xdr:colOff>179311</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>91848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>62</xdr:col>
-      <xdr:colOff>667905</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>78450</xdr:rowOff>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>667904</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1767550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2528,16 +2618,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>56</xdr:col>
+      <xdr:col>59</xdr:col>
       <xdr:colOff>757948</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>516525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>63</xdr:col>
+      <xdr:col>66</xdr:col>
       <xdr:colOff>819587</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>293565</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1621843</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2572,16 +2662,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>63</xdr:col>
+      <xdr:col>66</xdr:col>
       <xdr:colOff>20102</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>161444</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>67</xdr:col>
+      <xdr:col>70</xdr:col>
       <xdr:colOff>481778</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>228241</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>113941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2633,13 +2723,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>53</xdr:col>
+      <xdr:col>56</xdr:col>
       <xdr:colOff>392546</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>192578</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>68</xdr:col>
+      <xdr:col>71</xdr:col>
       <xdr:colOff>854363</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>332154</xdr:rowOff>
@@ -2711,16 +2801,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>653143</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>1052284</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>362857</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>281387</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>362856</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>268687</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2754,6 +2844,95 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3073,26 +3252,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839156C1-5CC4-40D4-892E-A723945E7391}">
-  <dimension ref="A1:AM207"/>
-  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AP207"/>
+  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="141" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="81" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="61.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="81" customWidth="1"/>
+    <col min="9" max="9" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="61.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3108,29 +3288,38 @@
       <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3147,28 +3336,37 @@
         <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="G2" s="3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H2" s="3" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -3185,31 +3383,40 @@
         <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="G3" s="3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H3" s="3" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -3226,31 +3433,40 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="G4" s="3" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="3" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -3267,28 +3483,33 @@
         <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -3304,29 +3525,32 @@
       <c r="E6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>49</v>
       </c>
@@ -3342,29 +3566,32 @@
       <c r="E7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>53</v>
       </c>
@@ -3380,29 +3607,32 @@
       <c r="E8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -3418,29 +3648,32 @@
       <c r="E9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="L9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -3456,29 +3689,32 @@
       <c r="E10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="M10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -3494,29 +3730,32 @@
       <c r="E11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -3532,29 +3771,32 @@
       <c r="E12" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="L12" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="M12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="O12" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>87</v>
       </c>
@@ -3570,29 +3812,32 @@
       <c r="E13" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="N13" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="O13" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>87</v>
       </c>
@@ -3608,29 +3853,32 @@
       <c r="E14" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="L14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="M14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="N14" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="O14" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>105</v>
       </c>
@@ -3646,29 +3894,32 @@
       <c r="E15" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="L15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="N15" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="O15" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>111</v>
       </c>
@@ -3684,29 +3935,32 @@
       <c r="E16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="O16" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -3722,29 +3976,32 @@
       <c r="E17" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="K17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="N17" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="O17" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>116</v>
       </c>
@@ -3760,29 +4017,32 @@
       <c r="E18" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="J18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="K18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="M18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="N18" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="O18" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>116</v>
       </c>
@@ -3798,29 +4058,32 @@
       <c r="E19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="K19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="N19" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="O19" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>12</v>
       </c>
@@ -3836,29 +4099,32 @@
       <c r="E20" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="K20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="L20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="M20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="N20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="O20" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
@@ -3874,29 +4140,32 @@
       <c r="E21" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="K21" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="L21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="N21" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="O21" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -3912,29 +4181,32 @@
       <c r="E22" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J22" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="O22" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>145</v>
       </c>
@@ -3950,29 +4222,32 @@
       <c r="E23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="L23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="N23" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="O23" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>145</v>
       </c>
@@ -3988,29 +4263,32 @@
       <c r="E24" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="J24" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="K24" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="L24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="N24" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="O24" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>145</v>
       </c>
@@ -4026,29 +4304,32 @@
       <c r="E25" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="J25" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="K25" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="L25" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="N25" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="L25" s="5" t="s">
+      <c r="O25" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>163</v>
       </c>
@@ -4064,29 +4345,32 @@
       <c r="E26" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="K26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="M26" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="N26" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="O26" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>163</v>
       </c>
@@ -4102,32 +4386,35 @@
       <c r="E27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="J27" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="K27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="M27" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="N27" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="O27" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AM27" t="s">
+      <c r="AP27" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>163</v>
       </c>
@@ -4143,29 +4430,32 @@
       <c r="E28" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="J28" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="K28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="M28" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="N28" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="O28" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>173</v>
       </c>
@@ -4181,32 +4471,35 @@
       <c r="E29" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="K29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="M29" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="N29" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="O29" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AM29" t="s">
+      <c r="AP29" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>173</v>
       </c>
@@ -4222,29 +4515,32 @@
       <c r="E30" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="J30" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="5" t="s">
+      <c r="K30" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="M30" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="N30" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="O30" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>173</v>
       </c>
@@ -4260,29 +4556,32 @@
       <c r="E31" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="J31" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="5" t="s">
+      <c r="K31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="M31" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="N31" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="O31" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>174</v>
       </c>
@@ -4298,29 +4597,32 @@
       <c r="E32" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="J32" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="K32" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="L32" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K32" s="5" t="s">
+      <c r="M32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L32" s="5" t="s">
+      <c r="O32" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>174</v>
       </c>
@@ -4336,29 +4638,32 @@
       <c r="E33" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="J33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="K33" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="L33" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K33" s="5" t="s">
+      <c r="M33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L33" s="5" t="s">
+      <c r="O33" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>174</v>
       </c>
@@ -4374,29 +4679,32 @@
       <c r="E34" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="K34" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="L34" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K34" s="5" t="s">
+      <c r="M34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L34" s="5" t="s">
+      <c r="O34" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>189</v>
       </c>
@@ -4412,15 +4720,9 @@
       <c r="E35" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
         <v>28</v>
       </c>
@@ -4428,13 +4730,22 @@
         <v>28</v>
       </c>
       <c r="K35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="O35" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>194</v>
       </c>
@@ -4450,15 +4761,9 @@
       <c r="E36" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
         <v>28</v>
       </c>
@@ -4466,13 +4771,22 @@
         <v>28</v>
       </c>
       <c r="K36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="O36" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>196</v>
       </c>
@@ -4488,15 +4802,9 @@
       <c r="E37" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
         <v>28</v>
       </c>
@@ -4504,13 +4812,22 @@
         <v>28</v>
       </c>
       <c r="K37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L37" s="5" t="s">
+      <c r="O37" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>197</v>
       </c>
@@ -4526,15 +4843,9 @@
       <c r="E38" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
         <v>28</v>
       </c>
@@ -4542,13 +4853,22 @@
         <v>28</v>
       </c>
       <c r="K38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L38" s="5" t="s">
+      <c r="O38" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>198</v>
       </c>
@@ -4564,15 +4884,9 @@
       <c r="E39" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
         <v>28</v>
       </c>
@@ -4580,13 +4894,22 @@
         <v>28</v>
       </c>
       <c r="K39" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L39" s="5" t="s">
+      <c r="O39" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>199</v>
       </c>
@@ -4602,15 +4925,9 @@
       <c r="E40" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
         <v>28</v>
       </c>
@@ -4618,13 +4935,22 @@
         <v>28</v>
       </c>
       <c r="K40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="O40" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>200</v>
       </c>
@@ -4640,15 +4966,9 @@
       <c r="E41" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
         <v>28</v>
       </c>
@@ -4656,13 +4976,22 @@
         <v>28</v>
       </c>
       <c r="K41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L41" s="5" t="s">
+      <c r="O41" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>201</v>
       </c>
@@ -4678,15 +5007,9 @@
       <c r="E42" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
         <v>28</v>
       </c>
@@ -4694,13 +5017,22 @@
         <v>28</v>
       </c>
       <c r="K42" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L42" s="5" t="s">
+      <c r="O42" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>202</v>
       </c>
@@ -4716,15 +5048,9 @@
       <c r="E43" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
         <v>28</v>
       </c>
@@ -4732,13 +5058,22 @@
         <v>28</v>
       </c>
       <c r="K43" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L43" s="5" t="s">
+      <c r="O43" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>205</v>
       </c>
@@ -4754,15 +5089,9 @@
       <c r="E44" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
         <v>28</v>
       </c>
@@ -4770,13 +5099,22 @@
         <v>28</v>
       </c>
       <c r="K44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="L44" s="5" t="s">
+      <c r="O44" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>206</v>
       </c>
@@ -4792,29 +5130,32 @@
       <c r="E45" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="J45" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="K45" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="L45" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K45" s="5" t="s">
+      <c r="M45" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="L45" s="5" t="s">
+      <c r="O45" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>206</v>
       </c>
@@ -4830,29 +5171,32 @@
       <c r="E46" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="K46" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="L46" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K46" s="5" t="s">
+      <c r="M46" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="L46" s="5" t="s">
+      <c r="O46" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>206</v>
       </c>
@@ -4868,29 +5212,32 @@
       <c r="E47" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="J47" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="K47" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="L47" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K47" s="5" t="s">
+      <c r="M47" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="L47" s="5" t="s">
+      <c r="O47" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>12</v>
       </c>
@@ -4906,29 +5253,32 @@
       <c r="E48" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="J48" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="K48" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" s="5" t="s">
+      <c r="L48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M48" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K48" s="5" t="s">
+      <c r="N48" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L48" s="5" t="s">
+      <c r="O48" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>12</v>
       </c>
@@ -4944,29 +5294,32 @@
       <c r="E49" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="J49" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="K49" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J49" s="5" t="s">
+      <c r="L49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M49" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="N49" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L49" s="5" t="s">
+      <c r="O49" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>12</v>
       </c>
@@ -4982,29 +5335,32 @@
       <c r="E50" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J50" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="K50" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" s="5" t="s">
+      <c r="L50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L50" s="5" t="s">
+      <c r="O50" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>12</v>
       </c>
@@ -5020,29 +5376,32 @@
       <c r="E51" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G51" s="5" t="s">
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="K51" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K51" s="5" t="s">
+      <c r="L51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L51" s="5" t="s">
+      <c r="O51" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>12</v>
       </c>
@@ -5058,29 +5417,32 @@
       <c r="E52" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="J52" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="K52" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J52" s="5" t="s">
+      <c r="L52" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M52" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K52" s="5" t="s">
+      <c r="N52" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L52" s="5" t="s">
+      <c r="O52" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>12</v>
       </c>
@@ -5096,29 +5458,32 @@
       <c r="E53" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="J53" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="K53" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J53" s="5" t="s">
+      <c r="L53" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="N53" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L53" s="5" t="s">
+      <c r="O53" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>12</v>
       </c>
@@ -5134,29 +5499,32 @@
       <c r="E54" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H54" s="5" t="s">
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K54" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K54" s="5" t="s">
+      <c r="L54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L54" s="5" t="s">
+      <c r="O54" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>12</v>
       </c>
@@ -5172,29 +5540,32 @@
       <c r="E55" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K55" s="5" t="s">
+      <c r="L55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N55" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L55" s="5" t="s">
+      <c r="O55" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>234</v>
       </c>
@@ -5210,29 +5581,32 @@
       <c r="E56" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="J56" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="K56" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="L56" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="J56" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K56" s="5" t="s">
+      <c r="M56" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N56" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="L56" s="5" t="s">
+      <c r="O56" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>245</v>
       </c>
@@ -5248,29 +5622,32 @@
       <c r="E57" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="J57" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="K57" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="I57" s="5" t="s">
+      <c r="L57" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="J57" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K57" s="5" t="s">
+      <c r="M57" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N57" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="L57" s="5" t="s">
+      <c r="O57" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>252</v>
       </c>
@@ -5286,29 +5663,32 @@
       <c r="E58" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" s="5" t="s">
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="H58" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" s="5" t="s">
+      <c r="K58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="M58" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K58" s="5" t="s">
+      <c r="N58" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L58" s="5" t="s">
+      <c r="O58" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>261</v>
       </c>
@@ -5324,29 +5704,32 @@
       <c r="E59" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G59" s="5" t="s">
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J59" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H59" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59" s="5" t="s">
+      <c r="K59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L59" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="M59" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K59" s="5" t="s">
+      <c r="N59" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L59" s="5" t="s">
+      <c r="O59" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>264</v>
       </c>
@@ -5362,15 +5745,9 @@
       <c r="E60" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
         <v>28</v>
       </c>
@@ -5378,13 +5755,22 @@
         <v>28</v>
       </c>
       <c r="K60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L60" s="5" t="s">
+      <c r="O60" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>267</v>
       </c>
@@ -5400,29 +5786,32 @@
       <c r="E61" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="6">
         <v>0.33</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="J61" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="H61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J61" s="5" t="s">
+      <c r="K61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K61" s="5" t="s">
+      <c r="N61" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L61" s="5" t="s">
+      <c r="O61" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>273</v>
       </c>
@@ -5438,29 +5827,32 @@
       <c r="E62" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="J62" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="H62" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J62" s="5" t="s">
+      <c r="K62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M62" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K62" s="5" t="s">
+      <c r="N62" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L62" s="5" t="s">
+      <c r="O62" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>273</v>
       </c>
@@ -5476,29 +5868,32 @@
       <c r="E63" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K63" s="5" t="s">
+      <c r="N63" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L63" s="5" t="s">
+      <c r="O63" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>273</v>
       </c>
@@ -5514,29 +5909,32 @@
       <c r="E64" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64" s="5" t="s">
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J64" s="5" t="s">
+      <c r="K64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M64" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="K64" s="5" t="s">
+      <c r="N64" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L64" s="5" t="s">
+      <c r="O64" s="5" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>273</v>
       </c>
@@ -5552,29 +5950,32 @@
       <c r="E65" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="7">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M65" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K65" s="5" t="s">
+      <c r="N65" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L65" s="5" t="s">
+      <c r="O65" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>273</v>
       </c>
@@ -5590,29 +5991,32 @@
       <c r="E66" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
       <c r="I66" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M66" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K66" s="5" t="s">
+      <c r="N66" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L66" s="5" t="s">
+      <c r="O66" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>273</v>
       </c>
@@ -5628,29 +6032,32 @@
       <c r="E67" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J67" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M67" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K67" s="5" t="s">
+      <c r="N67" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L67" s="5" t="s">
+      <c r="O67" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>273</v>
       </c>
@@ -5666,29 +6073,32 @@
       <c r="E68" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="J68" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H68" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J68" s="5" t="s">
+      <c r="K68" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M68" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K68" s="5" t="s">
+      <c r="N68" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L68" s="5" t="s">
+      <c r="O68" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>273</v>
       </c>
@@ -5704,29 +6114,32 @@
       <c r="E69" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K69" s="5" t="s">
+      <c r="N69" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L69" s="5" t="s">
+      <c r="O69" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>273</v>
       </c>
@@ -5742,29 +6155,32 @@
       <c r="E70" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="J70" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H70" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J70" s="5" t="s">
+      <c r="K70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K70" s="5" t="s">
+      <c r="N70" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L70" s="5" t="s">
+      <c r="O70" s="5" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>273</v>
       </c>
@@ -5780,29 +6196,32 @@
       <c r="E71" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F71" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G71" s="5" t="s">
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="H71" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J71" s="5" t="s">
+      <c r="K71" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M71" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K71" s="5" t="s">
+      <c r="N71" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L71" s="5" t="s">
+      <c r="O71" s="5" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>234</v>
       </c>
@@ -5818,29 +6237,32 @@
       <c r="E72" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G72" s="5" t="s">
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="K72" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I72" s="5" t="s">
+      <c r="L72" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="M72" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K72" s="5" t="s">
+      <c r="N72" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L72" s="5" t="s">
+      <c r="O72" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>273</v>
       </c>
@@ -5856,29 +6278,32 @@
       <c r="E73" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="J73" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H73" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J73" s="5" t="s">
+      <c r="K73" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K73" s="5" t="s">
+      <c r="N73" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L73" s="5" t="s">
+      <c r="O73" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>273</v>
       </c>
@@ -5894,29 +6319,32 @@
       <c r="E74" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="J74" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H74" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J74" s="5" t="s">
+      <c r="K74" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K74" s="5" t="s">
+      <c r="N74" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L74" s="5" t="s">
+      <c r="O74" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>273</v>
       </c>
@@ -5932,29 +6360,32 @@
       <c r="E75" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J75" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K75" s="5" t="s">
+      <c r="N75" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L75" s="5" t="s">
+      <c r="O75" s="5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>273</v>
       </c>
@@ -5970,29 +6401,32 @@
       <c r="E76" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J76" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K76" s="5" t="s">
+      <c r="N76" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L76" s="5" t="s">
+      <c r="O76" s="5" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>327</v>
       </c>
@@ -6008,29 +6442,32 @@
       <c r="E77" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="F77" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J77" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K77" s="5" t="s">
+      <c r="N77" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L77" s="5" t="s">
+      <c r="O77" s="5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>330</v>
       </c>
@@ -6046,29 +6483,32 @@
       <c r="E78" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F78" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
       <c r="I78" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J78" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K78" s="5" t="s">
+      <c r="N78" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L78" s="5" t="s">
+      <c r="O78" s="5" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>333</v>
       </c>
@@ -6084,29 +6524,32 @@
       <c r="E79" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F79" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
       <c r="I79" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M79" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K79" s="5" t="s">
+      <c r="N79" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L79" s="5" t="s">
+      <c r="O79" s="5" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>252</v>
       </c>
@@ -6122,29 +6565,32 @@
       <c r="E80" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G80" s="5" t="s">
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="H80" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I80" s="5" t="s">
+      <c r="K80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L80" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J80" s="5" t="s">
+      <c r="M80" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K80" s="5" t="s">
+      <c r="N80" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L80" s="5" t="s">
+      <c r="O80" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>261</v>
       </c>
@@ -6160,29 +6606,32 @@
       <c r="E81" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G81" s="5" t="s">
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J81" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H81" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I81" s="5" t="s">
+      <c r="K81" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L81" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J81" s="5" t="s">
+      <c r="M81" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K81" s="5" t="s">
+      <c r="N81" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L81" s="5" t="s">
+      <c r="O81" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>264</v>
       </c>
@@ -6198,15 +6647,9 @@
       <c r="E82" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
       <c r="I82" s="5" t="s">
         <v>28</v>
       </c>
@@ -6214,13 +6657,22 @@
         <v>28</v>
       </c>
       <c r="K82" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N82" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L82" s="5" t="s">
+      <c r="O82" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>334</v>
       </c>
@@ -6236,29 +6688,32 @@
       <c r="E83" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="6">
         <v>0.05</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="J83" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H83" s="5" t="s">
+      <c r="K83" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I83" s="5" t="s">
+      <c r="L83" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J83" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K83" s="5" t="s">
+      <c r="M83" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L83" s="5" t="s">
+      <c r="O83" s="5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>343</v>
       </c>
@@ -6274,29 +6729,32 @@
       <c r="E84" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="6">
         <v>0.05</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="J84" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H84" s="5" t="s">
+      <c r="K84" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I84" s="5" t="s">
+      <c r="L84" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J84" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K84" s="5" t="s">
+      <c r="M84" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N84" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L84" s="5" t="s">
+      <c r="O84" s="5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>344</v>
       </c>
@@ -6312,29 +6770,32 @@
       <c r="E85" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="6">
         <v>0.05</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="J85" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H85" s="5" t="s">
+      <c r="K85" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I85" s="5" t="s">
+      <c r="L85" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J85" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K85" s="5" t="s">
+      <c r="M85" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N85" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L85" s="5" t="s">
+      <c r="O85" s="5" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>345</v>
       </c>
@@ -6350,29 +6811,32 @@
       <c r="E86" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86" s="5" t="s">
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H86" s="5" t="s">
+      <c r="K86" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="I86" s="5" t="s">
+      <c r="L86" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J86" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K86" s="5" t="s">
+      <c r="M86" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N86" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L86" s="5" t="s">
+      <c r="O86" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>350</v>
       </c>
@@ -6388,29 +6852,32 @@
       <c r="E87" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="J87" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H87" s="5" t="s">
+      <c r="K87" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="L87" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J87" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K87" s="5" t="s">
+      <c r="M87" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N87" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L87" s="5" t="s">
+      <c r="O87" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>350</v>
       </c>
@@ -6426,29 +6893,32 @@
       <c r="E88" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="J88" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H88" s="5" t="s">
+      <c r="K88" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="I88" s="5" t="s">
+      <c r="L88" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J88" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K88" s="5" t="s">
+      <c r="M88" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N88" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L88" s="5" t="s">
+      <c r="O88" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>357</v>
       </c>
@@ -6464,29 +6934,32 @@
       <c r="E89" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="J89" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H89" s="5" t="s">
+      <c r="K89" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="I89" s="5" t="s">
+      <c r="L89" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J89" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K89" s="5" t="s">
+      <c r="M89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N89" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L89" s="5" t="s">
+      <c r="O89" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>361</v>
       </c>
@@ -6502,29 +6975,32 @@
       <c r="E90" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="J90" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H90" s="5" t="s">
+      <c r="K90" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="I90" s="5" t="s">
+      <c r="L90" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J90" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K90" s="5" t="s">
+      <c r="M90" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N90" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L90" s="5" t="s">
+      <c r="O90" s="5" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>361</v>
       </c>
@@ -6540,29 +7016,32 @@
       <c r="E91" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="J91" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H91" s="5" t="s">
+      <c r="K91" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="I91" s="5" t="s">
+      <c r="L91" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="J91" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K91" s="5" t="s">
+      <c r="M91" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N91" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="L91" s="5" t="s">
+      <c r="O91" s="5" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>366</v>
       </c>
@@ -6578,29 +7057,32 @@
       <c r="E92" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J92" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N92" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L92" s="5" t="s">
+      <c r="O92" s="5" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>273</v>
       </c>
@@ -6616,29 +7098,32 @@
       <c r="E93" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="F93" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G93" s="5" t="s">
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J93" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="H93" s="5" t="s">
+      <c r="K93" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="L93" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J93" s="5" t="s">
+      <c r="M93" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K93" s="5" t="s">
+      <c r="N93" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L93" s="5" t="s">
+      <c r="O93" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>273</v>
       </c>
@@ -6654,29 +7139,32 @@
       <c r="E94" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="J94" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="H94" s="5" t="s">
+      <c r="K94" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="I94" s="5" t="s">
+      <c r="L94" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J94" s="5" t="s">
+      <c r="M94" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K94" s="5" t="s">
+      <c r="N94" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="L94" s="5" t="s">
+      <c r="O94" s="5" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>384</v>
       </c>
@@ -6692,29 +7180,32 @@
       <c r="E95" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="J95" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H95" s="5" t="s">
+      <c r="K95" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="I95" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J95" s="5" t="s">
+      <c r="L95" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M95" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="K95" s="5" t="s">
+      <c r="N95" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="L95" s="5" t="s">
+      <c r="O95" s="5" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>384</v>
       </c>
@@ -6730,29 +7221,32 @@
       <c r="E96" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="F96" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G96" s="5" t="s">
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H96" s="5" t="s">
+      <c r="K96" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="I96" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J96" s="5" t="s">
+      <c r="L96" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M96" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K96" s="5" t="s">
+      <c r="N96" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="L96" s="5" t="s">
+      <c r="O96" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>12</v>
       </c>
@@ -6768,29 +7262,32 @@
       <c r="E97" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="J97" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="H97" s="5" t="s">
+      <c r="K97" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="I97" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J97" s="5" t="s">
+      <c r="L97" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M97" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K97" s="5" t="s">
+      <c r="N97" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="L97" s="5" t="s">
+      <c r="O97" s="5" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>401</v>
       </c>
@@ -6806,15 +7303,9 @@
       <c r="E98" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F98" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
       <c r="I98" s="5" t="s">
         <v>28</v>
       </c>
@@ -6822,13 +7313,22 @@
         <v>28</v>
       </c>
       <c r="K98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N98" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L98" s="5" t="s">
+      <c r="O98" s="5" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>404</v>
       </c>
@@ -6844,29 +7344,32 @@
       <c r="E99" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F99" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G99" s="5" t="s">
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="H99" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N99" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L99" s="5" t="s">
+      <c r="O99" s="5" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>410</v>
       </c>
@@ -6882,29 +7385,32 @@
       <c r="E100" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="F100" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" s="5" t="s">
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="H100" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="5" t="s">
+      <c r="K100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M100" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K100" s="5" t="s">
+      <c r="N100" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L100" s="5" t="s">
+      <c r="O100" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>415</v>
       </c>
@@ -6920,29 +7426,32 @@
       <c r="E101" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="F101" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G101" s="5" t="s">
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="H101" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I101" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J101" s="5" t="s">
+      <c r="K101" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L101" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M101" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K101" s="5" t="s">
+      <c r="N101" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L101" s="5" t="s">
+      <c r="O101" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>417</v>
       </c>
@@ -6958,29 +7467,32 @@
       <c r="E102" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="F102" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G102" s="5" t="s">
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J102" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="H102" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K102" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L102" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M102" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N102" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L102" s="5" t="s">
+      <c r="O102" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>423</v>
       </c>
@@ -6996,15 +7508,9 @@
       <c r="E103" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H103" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
       <c r="I103" s="5" t="s">
         <v>28</v>
       </c>
@@ -7012,13 +7518,22 @@
         <v>28</v>
       </c>
       <c r="K103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N103" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L103" s="5" t="s">
+      <c r="O103" s="5" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>428</v>
       </c>
@@ -7034,15 +7549,9 @@
       <c r="E104" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
       <c r="I104" s="5" t="s">
         <v>28</v>
       </c>
@@ -7050,13 +7559,22 @@
         <v>28</v>
       </c>
       <c r="K104" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L104" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N104" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L104" s="5" t="s">
+      <c r="O104" s="5" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>432</v>
       </c>
@@ -7072,29 +7590,32 @@
       <c r="E105" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="J105" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="H105" s="5" t="s">
+      <c r="K105" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="I105" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J105" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K105" s="5" t="s">
+      <c r="L105" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M105" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N105" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L105" s="5" t="s">
+      <c r="O105" s="5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>273</v>
       </c>
@@ -7110,15 +7631,9 @@
       <c r="E106" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
       <c r="I106" s="5" t="s">
         <v>28</v>
       </c>
@@ -7126,13 +7641,22 @@
         <v>28</v>
       </c>
       <c r="K106" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N106" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L106" s="5" t="s">
+      <c r="O106" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>273</v>
       </c>
@@ -7148,15 +7672,9 @@
       <c r="E107" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F107" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
       <c r="I107" s="5" t="s">
         <v>28</v>
       </c>
@@ -7164,13 +7682,22 @@
         <v>28</v>
       </c>
       <c r="K107" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L107" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M107" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N107" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L107" s="5" t="s">
+      <c r="O107" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>273</v>
       </c>
@@ -7186,15 +7713,9 @@
       <c r="E108" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F108" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
       <c r="I108" s="5" t="s">
         <v>28</v>
       </c>
@@ -7202,13 +7723,22 @@
         <v>28</v>
       </c>
       <c r="K108" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N108" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L108" s="5" t="s">
+      <c r="O108" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>273</v>
       </c>
@@ -7224,15 +7754,9 @@
       <c r="E109" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F109" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
       <c r="I109" s="5" t="s">
         <v>28</v>
       </c>
@@ -7240,13 +7764,22 @@
         <v>28</v>
       </c>
       <c r="K109" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M109" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N109" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L109" s="5" t="s">
+      <c r="O109" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>196</v>
       </c>
@@ -7262,29 +7795,32 @@
       <c r="E110" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F110" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
       <c r="I110" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J110" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L110" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M110" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K110" s="5" t="s">
+      <c r="N110" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L110" s="5" t="s">
+      <c r="O110" s="5" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>234</v>
       </c>
@@ -7300,29 +7836,32 @@
       <c r="E111" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="J111" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="H111" s="5" t="s">
+      <c r="K111" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I111" s="5" t="s">
+      <c r="L111" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="J111" s="5" t="s">
+      <c r="M111" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K111" s="5" t="s">
+      <c r="N111" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="L111" s="5" t="s">
+      <c r="O111" s="5" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>455</v>
       </c>
@@ -7338,29 +7877,32 @@
       <c r="E112" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="J112" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H112" s="5" t="s">
+      <c r="K112" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="I112" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J112" s="5" t="s">
+      <c r="L112" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M112" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K112" s="5" t="s">
+      <c r="N112" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="L112" s="5" t="s">
+      <c r="O112" s="5" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>464</v>
       </c>
@@ -7376,29 +7918,32 @@
       <c r="E113" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="J113" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H113" s="5" t="s">
+      <c r="K113" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="I113" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J113" s="5" t="s">
+      <c r="L113" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M113" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K113" s="5" t="s">
+      <c r="N113" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="L113" s="5" t="s">
+      <c r="O113" s="5" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>466</v>
       </c>
@@ -7414,29 +7959,32 @@
       <c r="E114" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="J114" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="H114" s="5" t="s">
+      <c r="K114" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="I114" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J114" s="5" t="s">
+      <c r="L114" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M114" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K114" s="5" t="s">
+      <c r="N114" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="L114" s="5" t="s">
+      <c r="O114" s="5" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>468</v>
       </c>
@@ -7452,29 +8000,32 @@
       <c r="E115" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G115" s="5" t="s">
+      <c r="J115" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H115" s="5" t="s">
+      <c r="K115" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="I115" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J115" s="5" t="s">
+      <c r="L115" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M115" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K115" s="5" t="s">
+      <c r="N115" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L115" s="5" t="s">
+      <c r="O115" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>474</v>
       </c>
@@ -7490,29 +8041,32 @@
       <c r="E116" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="J116" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H116" s="5" t="s">
+      <c r="K116" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="I116" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J116" s="5" t="s">
+      <c r="L116" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M116" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K116" s="5" t="s">
+      <c r="N116" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L116" s="5" t="s">
+      <c r="O116" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>476</v>
       </c>
@@ -7528,29 +8082,32 @@
       <c r="E117" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="J117" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H117" s="5" t="s">
+      <c r="K117" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="I117" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J117" s="5" t="s">
+      <c r="L117" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M117" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K117" s="5" t="s">
+      <c r="N117" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L117" s="5" t="s">
+      <c r="O117" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>478</v>
       </c>
@@ -7566,29 +8123,32 @@
       <c r="E118" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="J118" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H118" s="5" t="s">
+      <c r="K118" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="I118" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J118" s="5" t="s">
+      <c r="L118" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M118" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K118" s="5" t="s">
+      <c r="N118" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L118" s="5" t="s">
+      <c r="O118" s="5" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>481</v>
       </c>
@@ -7604,29 +8164,32 @@
       <c r="E119" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="J119" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H119" s="5" t="s">
+      <c r="K119" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="I119" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J119" s="5" t="s">
+      <c r="L119" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M119" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K119" s="5" t="s">
+      <c r="N119" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L119" s="5" t="s">
+      <c r="O119" s="5" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>273</v>
       </c>
@@ -7642,15 +8205,9 @@
       <c r="E120" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
       <c r="I120" s="5" t="s">
         <v>28</v>
       </c>
@@ -7658,13 +8215,22 @@
         <v>28</v>
       </c>
       <c r="K120" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L120" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M120" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N120" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L120" s="5" t="s">
+      <c r="O120" s="5" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>401</v>
       </c>
@@ -7680,15 +8246,9 @@
       <c r="E121" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F121" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G121" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
       <c r="I121" s="5" t="s">
         <v>28</v>
       </c>
@@ -7696,13 +8256,22 @@
         <v>28</v>
       </c>
       <c r="K121" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L121" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M121" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N121" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L121" s="5" t="s">
+      <c r="O121" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>489</v>
       </c>
@@ -7718,15 +8287,9 @@
       <c r="E122" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F122" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
       <c r="I122" s="5" t="s">
         <v>28</v>
       </c>
@@ -7734,13 +8297,22 @@
         <v>28</v>
       </c>
       <c r="K122" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L122" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N122" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L122" s="5" t="s">
+      <c r="O122" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>489</v>
       </c>
@@ -7756,15 +8328,9 @@
       <c r="E123" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F123" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H123" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
       <c r="I123" s="5" t="s">
         <v>28</v>
       </c>
@@ -7772,13 +8338,22 @@
         <v>28</v>
       </c>
       <c r="K123" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L123" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N123" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L123" s="5" t="s">
+      <c r="O123" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>489</v>
       </c>
@@ -7794,29 +8369,32 @@
       <c r="E124" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G124" s="5" t="s">
+      <c r="J124" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="H124" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J124" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K124" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L124" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N124" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L124" s="5" t="s">
+      <c r="O124" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>494</v>
       </c>
@@ -7832,29 +8410,32 @@
       <c r="E125" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="J125" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="H125" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I125" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J125" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K125" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L125" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M125" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N125" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L125" s="5" t="s">
+      <c r="O125" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>495</v>
       </c>
@@ -7870,15 +8451,9 @@
       <c r="E126" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="F126" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H126" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
       <c r="I126" s="5" t="s">
         <v>28</v>
       </c>
@@ -7886,13 +8461,22 @@
         <v>28</v>
       </c>
       <c r="K126" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L126" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M126" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N126" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="L126" s="5" t="s">
+      <c r="O126" s="5" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>499</v>
       </c>
@@ -7908,29 +8492,32 @@
       <c r="E127" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G127" s="5" t="s">
+      <c r="J127" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="H127" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I127" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J127" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K127" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L127" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M127" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N127" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="L127" s="5" t="s">
+      <c r="O127" s="5" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>506</v>
       </c>
@@ -7946,29 +8533,32 @@
       <c r="E128" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="7">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="J128" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H128" s="5" t="s">
+      <c r="K128" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="I128" s="5" t="s">
+      <c r="L128" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J128" s="5" t="s">
+      <c r="M128" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K128" s="5" t="s">
+      <c r="N128" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L128" s="5" t="s">
+      <c r="O128" s="5" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>510</v>
       </c>
@@ -7984,29 +8574,32 @@
       <c r="E129" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="F129" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H129" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
       <c r="I129" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J129" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K129" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L129" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M129" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K129" s="5" t="s">
+      <c r="N129" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L129" s="5" t="s">
+      <c r="O129" s="5" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>515</v>
       </c>
@@ -8022,29 +8615,32 @@
       <c r="E130" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G130" s="5" t="s">
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J130" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H130" s="5" t="s">
+      <c r="K130" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="I130" s="5" t="s">
+      <c r="L130" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J130" s="5" t="s">
+      <c r="M130" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="K130" s="5" t="s">
+      <c r="N130" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="L130" s="5" t="s">
+      <c r="O130" s="5" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>524</v>
       </c>
@@ -8060,29 +8656,32 @@
       <c r="E131" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F131" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G131" s="5" t="s">
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J131" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H131" s="5" t="s">
+      <c r="K131" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="I131" s="5" t="s">
+      <c r="L131" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="J131" s="5" t="s">
+      <c r="M131" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K131" s="5" t="s">
+      <c r="N131" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L131" s="5" t="s">
+      <c r="O131" s="5" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>532</v>
       </c>
@@ -8098,29 +8697,32 @@
       <c r="E132" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G132" s="5" t="s">
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="H132" s="5" t="s">
+      <c r="K132" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="I132" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J132" s="5" t="s">
+      <c r="L132" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M132" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K132" s="5" t="s">
+      <c r="N132" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L132" s="5" t="s">
+      <c r="O132" s="5" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>536</v>
       </c>
@@ -8136,29 +8738,32 @@
       <c r="E133" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H133" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
       <c r="I133" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J133" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K133" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L133" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M133" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K133" s="5" t="s">
+      <c r="N133" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L133" s="5" t="s">
+      <c r="O133" s="5" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>532</v>
       </c>
@@ -8174,29 +8779,32 @@
       <c r="E134" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G134" s="5" t="s">
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J134" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="H134" s="5" t="s">
+      <c r="K134" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="I134" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J134" s="5" t="s">
+      <c r="L134" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M134" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="K134" s="5" t="s">
+      <c r="N134" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L134" s="5" t="s">
+      <c r="O134" s="5" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>545</v>
       </c>
@@ -8212,29 +8820,32 @@
       <c r="E135" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="G135" s="5" t="s">
+      <c r="J135" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="H135" s="5" t="s">
+      <c r="K135" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="I135" s="5" t="s">
+      <c r="L135" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="J135" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K135" s="5" t="s">
+      <c r="M135" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N135" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L135" s="5" t="s">
+      <c r="O135" s="5" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>532</v>
       </c>
@@ -8250,29 +8861,32 @@
       <c r="E136" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="J136" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="H136" s="5" t="s">
+      <c r="K136" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="L136" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="J136" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K136" s="5" t="s">
+      <c r="M136" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N136" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="L136" s="5" t="s">
+      <c r="O136" s="5" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>66</v>
       </c>
@@ -8288,29 +8902,32 @@
       <c r="E137" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="J137" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="H137" s="5" t="s">
+      <c r="K137" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="L137" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J137" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K137" s="5" t="s">
+      <c r="M137" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N137" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L137" s="5" t="s">
+      <c r="O137" s="5" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>564</v>
       </c>
@@ -8326,29 +8943,32 @@
       <c r="E138" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="F138" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G138" s="5" t="s">
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J138" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="H138" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I138" s="5" t="s">
+      <c r="K138" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L138" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="J138" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K138" s="5" t="s">
+      <c r="M138" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N138" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L138" s="5" t="s">
+      <c r="O138" s="5" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>12</v>
       </c>
@@ -8364,29 +8984,32 @@
       <c r="E139" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I139" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J139" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K139" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L139" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N139" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L139" s="5" t="s">
+      <c r="O139" s="5" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>573</v>
       </c>
@@ -8402,29 +9025,32 @@
       <c r="E140" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="J140" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="H140" s="5" t="s">
+      <c r="K140" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="I140" s="5" t="s">
+      <c r="L140" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="J140" s="5" t="s">
+      <c r="M140" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K140" s="5" t="s">
+      <c r="N140" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="L140" s="5" t="s">
+      <c r="O140" s="5" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>583</v>
       </c>
@@ -8440,29 +9066,32 @@
       <c r="E141" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="G141" s="5" t="s">
+      <c r="J141" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="H141" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I141" s="5" t="s">
+      <c r="K141" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L141" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="J141" s="5" t="s">
+      <c r="M141" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K141" s="5" t="s">
+      <c r="N141" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="L141" s="5" t="s">
+      <c r="O141" s="5" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>583</v>
       </c>
@@ -8478,29 +9107,32 @@
       <c r="E142" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="G142" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H142" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J142" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K142" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L142" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M142" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N142" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="L142" s="5" t="s">
+      <c r="O142" s="5" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>206</v>
       </c>
@@ -8516,29 +9148,32 @@
       <c r="E143" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G143" s="5" t="s">
+      <c r="J143" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="H143" s="5" t="s">
+      <c r="K143" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="I143" s="5" t="s">
+      <c r="L143" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="J143" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K143" s="5" t="s">
+      <c r="M143" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N143" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="L143" s="5" t="s">
+      <c r="O143" s="5" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>273</v>
       </c>
@@ -8554,29 +9189,32 @@
       <c r="E144" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="J144" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H144" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I144" s="5" t="s">
+      <c r="K144" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L144" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="J144" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K144" s="5" t="s">
+      <c r="M144" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N144" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="L144" s="5" t="s">
+      <c r="O144" s="5" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>24</v>
       </c>
@@ -8592,29 +9230,32 @@
       <c r="E145" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G145" s="5" t="s">
+      <c r="J145" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H145" s="5" t="s">
+      <c r="K145" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="I145" s="5" t="s">
+      <c r="L145" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="J145" s="5" t="s">
+      <c r="M145" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K145" s="5" t="s">
+      <c r="N145" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L145" s="5" t="s">
+      <c r="O145" s="5" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>605</v>
       </c>
@@ -8630,29 +9271,32 @@
       <c r="E146" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G146" s="5" t="s">
+      <c r="J146" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="H146" s="5" t="s">
+      <c r="K146" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I146" s="5" t="s">
+      <c r="L146" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J146" s="5" t="s">
+      <c r="M146" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K146" s="5" t="s">
+      <c r="N146" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L146" s="5" t="s">
+      <c r="O146" s="5" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>605</v>
       </c>
@@ -8668,29 +9312,32 @@
       <c r="E147" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F147" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G147" s="5" t="s">
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J147" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="K147" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I147" s="5" t="s">
+      <c r="L147" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J147" s="5" t="s">
+      <c r="M147" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K147" s="5" t="s">
+      <c r="N147" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L147" s="5" t="s">
+      <c r="O147" s="5" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>605</v>
       </c>
@@ -8706,29 +9353,32 @@
       <c r="E148" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="J148" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H148" s="5" t="s">
+      <c r="K148" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="I148" s="5" t="s">
+      <c r="L148" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="J148" s="5" t="s">
+      <c r="M148" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K148" s="5" t="s">
+      <c r="N148" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L148" s="5" t="s">
+      <c r="O148" s="5" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>605</v>
       </c>
@@ -8744,29 +9394,32 @@
       <c r="E149" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F149" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G149" s="5" t="s">
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J149" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="H149" s="5" t="s">
+      <c r="K149" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I149" s="5" t="s">
+      <c r="L149" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J149" s="5" t="s">
+      <c r="M149" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K149" s="5" t="s">
+      <c r="N149" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L149" s="5" t="s">
+      <c r="O149" s="5" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>12</v>
       </c>
@@ -8782,15 +9435,9 @@
       <c r="E150" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F150" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
       <c r="I150" s="5" t="s">
         <v>28</v>
       </c>
@@ -8798,13 +9445,22 @@
         <v>28</v>
       </c>
       <c r="K150" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L150" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M150" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N150" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L150" s="5" t="s">
+      <c r="O150" s="5" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>617</v>
       </c>
@@ -8820,15 +9476,9 @@
       <c r="E151" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F151" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H151" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
       <c r="I151" s="5" t="s">
         <v>28</v>
       </c>
@@ -8836,13 +9486,22 @@
         <v>28</v>
       </c>
       <c r="K151" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L151" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M151" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N151" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L151" s="5" t="s">
+      <c r="O151" s="5" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>621</v>
       </c>
@@ -8858,15 +9517,9 @@
       <c r="E152" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="F152" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
       <c r="I152" s="5" t="s">
         <v>28</v>
       </c>
@@ -8874,13 +9527,22 @@
         <v>28</v>
       </c>
       <c r="K152" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L152" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M152" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L152" s="5" t="s">
+      <c r="O152" s="5" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>111</v>
       </c>
@@ -8896,15 +9558,9 @@
       <c r="E153" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="F153" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
       <c r="I153" s="5" t="s">
         <v>28</v>
       </c>
@@ -8912,13 +9568,22 @@
         <v>28</v>
       </c>
       <c r="K153" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L153" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M153" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L153" s="5" t="s">
+      <c r="O153" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>489</v>
       </c>
@@ -8934,29 +9599,32 @@
       <c r="E154" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G154" s="5" t="s">
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J154" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H154" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I154" s="5" t="s">
+      <c r="K154" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L154" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="J154" s="5" t="s">
+      <c r="M154" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K154" s="5" t="s">
+      <c r="N154" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="L154" s="5" t="s">
+      <c r="O154" s="5" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>489</v>
       </c>
@@ -8972,29 +9640,32 @@
       <c r="E155" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="F155" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G155" s="5" t="s">
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J155" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="H155" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I155" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J155" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K155" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L155" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M155" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N155" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="L155" s="5" t="s">
+      <c r="O155" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>489</v>
       </c>
@@ -9010,15 +9681,9 @@
       <c r="E156" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="F156" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G156" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H156" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
       <c r="I156" s="5" t="s">
         <v>28</v>
       </c>
@@ -9026,13 +9691,22 @@
         <v>28</v>
       </c>
       <c r="K156" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L156" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M156" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N156" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="L156" s="5" t="s">
+      <c r="O156" s="5" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>404</v>
       </c>
@@ -9048,15 +9722,9 @@
       <c r="E157" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H157" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
       <c r="I157" s="5" t="s">
         <v>28</v>
       </c>
@@ -9064,13 +9732,22 @@
         <v>28</v>
       </c>
       <c r="K157" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L157" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M157" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N157" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="L157" s="5" t="s">
+      <c r="O157" s="5" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>273</v>
       </c>
@@ -9086,29 +9763,32 @@
       <c r="E158" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="J158" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H158" s="5" t="s">
+      <c r="K158" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I158" s="5" t="s">
+      <c r="L158" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="J158" s="5" t="s">
+      <c r="M158" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K158" s="5" t="s">
+      <c r="N158" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L158" s="5" t="s">
+      <c r="O158" s="5" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>648</v>
       </c>
@@ -9124,29 +9804,32 @@
       <c r="E159" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="G159" s="5" t="s">
+      <c r="J159" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H159" s="5" t="s">
+      <c r="K159" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="I159" s="5" t="s">
+      <c r="L159" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="J159" s="5" t="s">
+      <c r="M159" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K159" s="5" t="s">
+      <c r="N159" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L159" s="5" t="s">
+      <c r="O159" s="5" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>273</v>
       </c>
@@ -9162,15 +9845,9 @@
       <c r="E160" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H160" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
       <c r="I160" s="5" t="s">
         <v>28</v>
       </c>
@@ -9178,13 +9855,22 @@
         <v>28</v>
       </c>
       <c r="K160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N160" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L160" s="5" t="s">
+      <c r="O160" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>273</v>
       </c>
@@ -9200,15 +9886,9 @@
       <c r="E161" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H161" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
       <c r="I161" s="5" t="s">
         <v>28</v>
       </c>
@@ -9216,13 +9896,22 @@
         <v>28</v>
       </c>
       <c r="K161" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L161" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M161" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N161" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L161" s="5" t="s">
+      <c r="O161" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>657</v>
       </c>
@@ -9238,15 +9927,9 @@
       <c r="E162" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F162" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H162" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
       <c r="I162" s="5" t="s">
         <v>28</v>
       </c>
@@ -9254,13 +9937,22 @@
         <v>28</v>
       </c>
       <c r="K162" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L162" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M162" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N162" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L162" s="5" t="s">
+      <c r="O162" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>105</v>
       </c>
@@ -9276,15 +9968,9 @@
       <c r="E163" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F163" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H163" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
+      <c r="H163" s="5"/>
       <c r="I163" s="5" t="s">
         <v>28</v>
       </c>
@@ -9292,13 +9978,22 @@
         <v>28</v>
       </c>
       <c r="K163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N163" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L163" s="5" t="s">
+      <c r="O163" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>87</v>
       </c>
@@ -9314,15 +10009,9 @@
       <c r="E164" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F164" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H164" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
       <c r="I164" s="5" t="s">
         <v>28</v>
       </c>
@@ -9330,13 +10019,22 @@
         <v>28</v>
       </c>
       <c r="K164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L164" s="5" t="s">
+      <c r="O164" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>659</v>
       </c>
@@ -9352,15 +10050,9 @@
       <c r="E165" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F165" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
       <c r="I165" s="5" t="s">
         <v>28</v>
       </c>
@@ -9368,13 +10060,22 @@
         <v>28</v>
       </c>
       <c r="K165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L165" s="5" t="s">
+      <c r="O165" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>660</v>
       </c>
@@ -9390,15 +10091,9 @@
       <c r="E166" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F166" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H166" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
       <c r="I166" s="5" t="s">
         <v>28</v>
       </c>
@@ -9406,13 +10101,22 @@
         <v>28</v>
       </c>
       <c r="K166" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L166" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M166" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L166" s="5" t="s">
+      <c r="O166" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>661</v>
       </c>
@@ -9428,15 +10132,9 @@
       <c r="E167" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="F167" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
       <c r="I167" s="5" t="s">
         <v>28</v>
       </c>
@@ -9444,13 +10142,22 @@
         <v>28</v>
       </c>
       <c r="K167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N167" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L167" s="5" t="s">
+      <c r="O167" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>116</v>
       </c>
@@ -9466,29 +10173,32 @@
       <c r="E168" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="G168" s="5" t="s">
+      <c r="J168" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H168" s="5" t="s">
+      <c r="K168" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="I168" s="5" t="s">
+      <c r="L168" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="J168" s="5" t="s">
+      <c r="M168" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K168" s="5" t="s">
+      <c r="N168" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L168" s="5" t="s">
+      <c r="O168" s="5" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>666</v>
       </c>
@@ -9504,29 +10214,32 @@
       <c r="E169" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="J169" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H169" s="5" t="s">
+      <c r="K169" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="I169" s="5" t="s">
+      <c r="L169" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="J169" s="5" t="s">
+      <c r="M169" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K169" s="5" t="s">
+      <c r="N169" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L169" s="5" t="s">
+      <c r="O169" s="5" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>273</v>
       </c>
@@ -9542,15 +10255,9 @@
       <c r="E170" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="F170" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H170" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
       <c r="I170" s="5" t="s">
         <v>28</v>
       </c>
@@ -9558,13 +10265,22 @@
         <v>28</v>
       </c>
       <c r="K170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N170" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L170" s="5" t="s">
+      <c r="O170" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>273</v>
       </c>
@@ -9580,15 +10296,9 @@
       <c r="E171" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="F171" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H171" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
       <c r="I171" s="5" t="s">
         <v>28</v>
       </c>
@@ -9596,13 +10306,22 @@
         <v>28</v>
       </c>
       <c r="K171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N171" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L171" s="5" t="s">
+      <c r="O171" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>657</v>
       </c>
@@ -9618,15 +10337,9 @@
       <c r="E172" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
       <c r="I172" s="5" t="s">
         <v>28</v>
       </c>
@@ -9634,13 +10347,22 @@
         <v>28</v>
       </c>
       <c r="K172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N172" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L172" s="5" t="s">
+      <c r="O172" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>105</v>
       </c>
@@ -9656,15 +10378,9 @@
       <c r="E173" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F173" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
       <c r="I173" s="5" t="s">
         <v>28</v>
       </c>
@@ -9672,13 +10388,22 @@
         <v>28</v>
       </c>
       <c r="K173" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L173" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M173" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N173" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L173" s="5" t="s">
+      <c r="O173" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>87</v>
       </c>
@@ -9694,15 +10419,9 @@
       <c r="E174" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H174" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
       <c r="I174" s="5" t="s">
         <v>28</v>
       </c>
@@ -9710,13 +10429,22 @@
         <v>28</v>
       </c>
       <c r="K174" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L174" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M174" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N174" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L174" s="5" t="s">
+      <c r="O174" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>659</v>
       </c>
@@ -9732,15 +10460,9 @@
       <c r="E175" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F175" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H175" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
       <c r="I175" s="5" t="s">
         <v>28</v>
       </c>
@@ -9748,13 +10470,22 @@
         <v>28</v>
       </c>
       <c r="K175" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L175" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M175" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N175" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L175" s="5" t="s">
+      <c r="O175" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>660</v>
       </c>
@@ -9770,15 +10501,9 @@
       <c r="E176" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F176" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H176" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
       <c r="I176" s="5" t="s">
         <v>28</v>
       </c>
@@ -9786,13 +10511,22 @@
         <v>28</v>
       </c>
       <c r="K176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L176" s="5" t="s">
+      <c r="O176" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>661</v>
       </c>
@@ -9808,15 +10542,9 @@
       <c r="E177" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="H177" s="5"/>
       <c r="I177" s="5" t="s">
         <v>28</v>
       </c>
@@ -9824,13 +10552,22 @@
         <v>28</v>
       </c>
       <c r="K177" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L177" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M177" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="L177" s="5" t="s">
+      <c r="O177" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>661</v>
       </c>
@@ -9846,29 +10583,32 @@
       <c r="E178" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="F178" s="6">
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="6">
         <v>0.33</v>
       </c>
-      <c r="G178" s="5" t="s">
+      <c r="J178" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H178" s="5" t="s">
+      <c r="K178" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="I178" s="5" t="s">
+      <c r="L178" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="J178" s="5" t="s">
+      <c r="M178" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K178" s="5" t="s">
+      <c r="N178" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="L178" s="5" t="s">
+      <c r="O178" s="5" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>676</v>
       </c>
@@ -9884,15 +10624,9 @@
       <c r="E179" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F179" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H179" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F179" s="5"/>
+      <c r="G179" s="5"/>
+      <c r="H179" s="5"/>
       <c r="I179" s="5" t="s">
         <v>28</v>
       </c>
@@ -9900,13 +10634,22 @@
         <v>28</v>
       </c>
       <c r="K179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N179" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="L179" s="5" t="s">
+      <c r="O179" s="5" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>661</v>
       </c>
@@ -9922,29 +10665,32 @@
       <c r="E180" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" s="5"/>
+      <c r="G180" s="5"/>
+      <c r="H180" s="5"/>
+      <c r="I180" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="G180" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H180" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I180" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M180" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K180" s="5" t="s">
+      <c r="N180" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="L180" s="5" t="s">
+      <c r="O180" s="5" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>401</v>
       </c>
@@ -9960,15 +10706,9 @@
       <c r="E181" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F181" s="5"/>
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
       <c r="I181" s="5" t="s">
         <v>28</v>
       </c>
@@ -9976,13 +10716,22 @@
         <v>28</v>
       </c>
       <c r="K181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N181" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="L181" s="5" t="s">
+      <c r="O181" s="5" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>12</v>
       </c>
@@ -9998,15 +10747,9 @@
       <c r="E182" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="F182" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F182" s="5"/>
+      <c r="G182" s="5"/>
+      <c r="H182" s="5"/>
       <c r="I182" s="5" t="s">
         <v>28</v>
       </c>
@@ -10014,13 +10757,22 @@
         <v>28</v>
       </c>
       <c r="K182" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L182" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M182" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N182" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="L182" s="5" t="s">
+      <c r="O182" s="5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>687</v>
       </c>
@@ -10036,15 +10788,9 @@
       <c r="E183" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F183" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H183" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
       <c r="I183" s="5" t="s">
         <v>28</v>
       </c>
@@ -10052,13 +10798,22 @@
         <v>28</v>
       </c>
       <c r="K183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N183" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="L183" s="5" t="s">
+      <c r="O183" s="5" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>688</v>
       </c>
@@ -10074,29 +10829,32 @@
       <c r="E184" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="J184" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="H184" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I184" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J184" s="5" t="s">
+      <c r="K184" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L184" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M184" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="K184" s="5" t="s">
+      <c r="N184" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="L184" s="5" t="s">
+      <c r="O184" s="5" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>695</v>
       </c>
@@ -10112,29 +10870,32 @@
       <c r="E185" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G185" s="5" t="s">
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J185" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="H185" s="5" t="s">
+      <c r="K185" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="I185" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J185" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K185" s="5" t="s">
+      <c r="L185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N185" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="L185" s="5" t="s">
+      <c r="O185" s="5" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>404</v>
       </c>
@@ -10150,29 +10911,32 @@
       <c r="E186" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G186" s="5" t="s">
+      <c r="J186" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H186" s="5" t="s">
+      <c r="K186" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="I186" s="5" t="s">
+      <c r="L186" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J186" s="5" t="s">
+      <c r="M186" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K186" s="5" t="s">
+      <c r="N186" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L186" s="5" t="s">
+      <c r="O186" s="5" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>404</v>
       </c>
@@ -10188,29 +10952,32 @@
       <c r="E187" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G187" s="5" t="s">
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+      <c r="I187" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J187" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H187" s="5" t="s">
+      <c r="K187" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="I187" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J187" s="5" t="s">
+      <c r="L187" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M187" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K187" s="5" t="s">
+      <c r="N187" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L187" s="5" t="s">
+      <c r="O187" s="5" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>704</v>
       </c>
@@ -10226,29 +10993,32 @@
       <c r="E188" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F188" s="5" t="s">
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="G188" s="5" t="s">
+      <c r="J188" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H188" s="5" t="s">
+      <c r="K188" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="I188" s="5" t="s">
+      <c r="L188" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J188" s="5" t="s">
+      <c r="M188" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K188" s="5" t="s">
+      <c r="N188" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L188" s="5" t="s">
+      <c r="O188" s="5" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>704</v>
       </c>
@@ -10264,29 +11034,32 @@
       <c r="E189" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F189" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G189" s="5" t="s">
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J189" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H189" s="5" t="s">
+      <c r="K189" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="I189" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J189" s="5" t="s">
+      <c r="L189" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M189" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K189" s="5" t="s">
+      <c r="N189" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L189" s="5" t="s">
+      <c r="O189" s="5" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>706</v>
       </c>
@@ -10302,29 +11075,32 @@
       <c r="E190" s="5" t="s">
         <v>707</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G190" s="5" t="s">
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+      <c r="I190" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J190" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="H190" s="5" t="s">
+      <c r="K190" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="I190" s="5" t="s">
+      <c r="L190" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J190" s="5" t="s">
+      <c r="M190" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K190" s="5" t="s">
+      <c r="N190" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L190" s="5" t="s">
+      <c r="O190" s="5" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>709</v>
       </c>
@@ -10340,29 +11116,32 @@
       <c r="E191" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="F191" s="6">
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
+      <c r="I191" s="6">
         <v>0.22</v>
       </c>
-      <c r="G191" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H191" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I191" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J191" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K191" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L191" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M191" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K191" s="5" t="s">
+      <c r="N191" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L191" s="5" t="s">
+      <c r="O191" s="5" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>713</v>
       </c>
@@ -10378,29 +11157,32 @@
       <c r="E192" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="F192" s="6">
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="6">
         <v>0.13</v>
       </c>
-      <c r="G192" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H192" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I192" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J192" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K192" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L192" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M192" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K192" s="5" t="s">
+      <c r="N192" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L192" s="5" t="s">
+      <c r="O192" s="5" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>718</v>
       </c>
@@ -10416,29 +11198,32 @@
       <c r="E193" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="F193" s="5" t="s">
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="G193" s="5" t="s">
+      <c r="J193" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="H193" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I193" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J193" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="K193" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L193" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M193" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N193" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L193" s="5" t="s">
+      <c r="O193" s="5" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>404</v>
       </c>
@@ -10454,29 +11239,32 @@
       <c r="E194" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="F194" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G194" s="5" t="s">
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J194" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H194" s="5" t="s">
+      <c r="K194" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="I194" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J194" s="5" t="s">
+      <c r="L194" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M194" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="K194" s="5" t="s">
+      <c r="N194" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L194" s="5" t="s">
+      <c r="O194" s="5" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>729</v>
       </c>
@@ -10492,29 +11280,32 @@
       <c r="E195" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="F195" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G195" s="5" t="s">
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J195" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H195" s="5" t="s">
+      <c r="K195" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="I195" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J195" s="5" t="s">
+      <c r="L195" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M195" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="K195" s="5" t="s">
+      <c r="N195" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L195" s="5" t="s">
+      <c r="O195" s="5" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>605</v>
       </c>
@@ -10530,29 +11321,32 @@
       <c r="E196" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G196" s="5" t="s">
+      <c r="J196" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H196" s="5" t="s">
+      <c r="K196" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I196" s="5" t="s">
+      <c r="L196" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J196" s="5" t="s">
+      <c r="M196" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K196" s="5" t="s">
+      <c r="N196" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L196" s="5" t="s">
+      <c r="O196" s="5" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>605</v>
       </c>
@@ -10568,29 +11362,32 @@
       <c r="E197" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F197" s="5" t="s">
+      <c r="F197" s="5"/>
+      <c r="G197" s="5"/>
+      <c r="H197" s="5"/>
+      <c r="I197" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G197" s="5" t="s">
+      <c r="J197" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H197" s="5" t="s">
+      <c r="K197" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="I197" s="5" t="s">
+      <c r="L197" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="J197" s="5" t="s">
+      <c r="M197" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K197" s="5" t="s">
+      <c r="N197" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L197" s="5" t="s">
+      <c r="O197" s="5" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>605</v>
       </c>
@@ -10606,29 +11403,32 @@
       <c r="E198" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+      <c r="I198" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="J198" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H198" s="5" t="s">
+      <c r="K198" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="I198" s="5" t="s">
+      <c r="L198" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="J198" s="5" t="s">
+      <c r="M198" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K198" s="5" t="s">
+      <c r="N198" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L198" s="5" t="s">
+      <c r="O198" s="5" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>605</v>
       </c>
@@ -10644,29 +11444,32 @@
       <c r="E199" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F199" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G199" s="5" t="s">
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J199" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H199" s="5" t="s">
+      <c r="K199" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I199" s="5" t="s">
+      <c r="L199" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J199" s="5" t="s">
+      <c r="M199" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K199" s="5" t="s">
+      <c r="N199" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L199" s="5" t="s">
+      <c r="O199" s="5" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>605</v>
       </c>
@@ -10682,29 +11485,32 @@
       <c r="E200" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="F200" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G200" s="5" t="s">
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J200" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H200" s="5" t="s">
+      <c r="K200" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I200" s="5" t="s">
+      <c r="L200" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="J200" s="5" t="s">
+      <c r="M200" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K200" s="5" t="s">
+      <c r="N200" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L200" s="5" t="s">
+      <c r="O200" s="5" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>404</v>
       </c>
@@ -10720,29 +11526,32 @@
       <c r="E201" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="F201" s="5" t="s">
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+      <c r="I201" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="G201" s="5" t="s">
+      <c r="J201" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="H201" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I201" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J201" s="5" t="s">
+      <c r="K201" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L201" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M201" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K201" s="5" t="s">
+      <c r="N201" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="L201" s="5" t="s">
+      <c r="O201" s="5" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>744</v>
       </c>
@@ -10758,29 +11567,32 @@
       <c r="E202" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="F202" s="5" t="s">
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+      <c r="H202" s="5"/>
+      <c r="I202" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="G202" s="5" t="s">
+      <c r="J202" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="H202" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I202" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J202" s="5" t="s">
+      <c r="K202" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L202" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M202" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K202" s="5" t="s">
+      <c r="N202" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="L202" s="5" t="s">
+      <c r="O202" s="5" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>474</v>
       </c>
@@ -10796,29 +11608,32 @@
       <c r="E203" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="H203" s="5"/>
+      <c r="I203" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="J203" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="H203" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I203" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J203" s="5" t="s">
+      <c r="K203" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L203" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M203" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K203" s="5" t="s">
+      <c r="N203" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="L203" s="5" t="s">
+      <c r="O203" s="5" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>747</v>
       </c>
@@ -10834,29 +11649,32 @@
       <c r="E204" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="F204" s="5" t="s">
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="G204" s="5" t="s">
+      <c r="J204" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="H204" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I204" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J204" s="5" t="s">
+      <c r="K204" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L204" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M204" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K204" s="5" t="s">
+      <c r="N204" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="L204" s="5" t="s">
+      <c r="O204" s="5" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>401</v>
       </c>
@@ -10872,29 +11690,32 @@
       <c r="E205" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="F205" s="6">
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="6">
         <v>0.23</v>
       </c>
-      <c r="G205" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H205" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I205" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="J205" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L205" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M205" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K205" s="5" t="s">
+      <c r="N205" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="L205" s="5" t="s">
+      <c r="O205" s="5" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>753</v>
       </c>
@@ -10910,29 +11731,32 @@
       <c r="E206" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F206" s="5" t="s">
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+      <c r="I206" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G206" s="5" t="s">
+      <c r="J206" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="H206" s="5" t="s">
+      <c r="K206" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I206" s="5" t="s">
+      <c r="L206" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J206" s="5" t="s">
+      <c r="M206" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K206" s="5" t="s">
+      <c r="N206" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L206" s="5" t="s">
+      <c r="O206" s="5" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>757</v>
       </c>
@@ -10948,25 +11772,28 @@
       <c r="E207" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="F207" s="7">
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="7">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G207" s="5" t="s">
+      <c r="J207" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H207" s="5" t="s">
+      <c r="K207" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="I207" s="5" t="s">
+      <c r="L207" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J207" s="5" t="s">
+      <c r="M207" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K207" s="5" t="s">
+      <c r="N207" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L207" s="5" t="s">
+      <c r="O207" s="5" t="s">
         <v>760</v>
       </c>
     </row>
